--- a/output/relatorio.xlsx
+++ b/output/relatorio.xlsx
@@ -30524,7 +30524,7 @@
         <v>1</v>
       </c>
       <c r="H792" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="793">
@@ -32311,7 +32311,7 @@
         <v>1</v>
       </c>
       <c r="H839" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="840">
@@ -34089,7 +34089,7 @@
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>S/ VENDEDOR</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">

--- a/output/relatorio.xlsx
+++ b/output/relatorio.xlsx
@@ -13529,7 +13529,7 @@
         <v>1</v>
       </c>
       <c r="H345" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -24600,7 +24600,7 @@
         <v>1</v>
       </c>
       <c r="H636" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="637">

--- a/output/relatorio.xlsx
+++ b/output/relatorio.xlsx
@@ -18965,7 +18965,7 @@
         <v>1</v>
       </c>
       <c r="H488" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="489">
@@ -36844,7 +36844,7 @@
         <v>1</v>
       </c>
       <c r="H958" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="959">

--- a/output/relatorio.xlsx
+++ b/output/relatorio.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1023"/>
+  <dimension ref="A1:H1024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37572,17 +37572,17 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>f457e4ec-f7a6-41f3-a1aa-8cec2e39859f</t>
+          <t>f456a253-e8d4-4f59-ad55-3df660edfa96</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>Ynvest Solar</t>
+          <t>Rafael Mattos</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com comercial</t>
         </is>
       </c>
       <c r="D978" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="E978" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>RAFAELA PEREIRA DE MENEZES</t>
         </is>
       </c>
       <c r="F978" t="inlineStr">
@@ -37604,23 +37604,23 @@
         <v>1</v>
       </c>
       <c r="H978" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>f45cd5f0-6c50-406b-a0e9-3f413733a63b</t>
+          <t>f457e4ec-f7a6-41f3-a1aa-8cec2e39859f</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Vinicius Santos</t>
+          <t>Ynvest Solar</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D979" t="inlineStr">
@@ -37630,7 +37630,7 @@
       </c>
       <c r="E979" t="inlineStr">
         <is>
-          <t>RAFAELA PEREIRA DE MENEZES</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F979" t="inlineStr">
@@ -37642,33 +37642,33 @@
         <v>1</v>
       </c>
       <c r="H979" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>f47f89b9-83ae-49bd-a220-62319ec3d7f1</t>
+          <t>f45cd5f0-6c50-406b-a0e9-3f413733a63b</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>Lauri Oliveira</t>
+          <t>Vinicius Santos</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D980" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E980" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>RAFAELA PEREIRA DE MENEZES</t>
         </is>
       </c>
       <c r="F980" t="inlineStr">
@@ -37680,33 +37680,33 @@
         <v>1</v>
       </c>
       <c r="H980" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>f4fa3264-c1f9-425c-924a-90aff6c5e555</t>
+          <t>f47f89b9-83ae-49bd-a220-62319ec3d7f1</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>CÉSAR LUCAS BARBOSA</t>
+          <t>Lauri Oliveira</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>RAFAELA PEREIRA DE MENEZES</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
@@ -37718,18 +37718,18 @@
         <v>1</v>
       </c>
       <c r="H981" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>f52bff3e-a5ad-47c9-8eda-04fd6b2bddd5</t>
+          <t>f4fa3264-c1f9-425c-924a-90aff6c5e555</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>Robson Del Sante Cancelier</t>
+          <t>CÉSAR LUCAS BARBOSA</t>
         </is>
       </c>
       <c r="C982" t="inlineStr">
@@ -37739,7 +37739,7 @@
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E982" t="inlineStr">
@@ -37756,33 +37756,33 @@
         <v>1</v>
       </c>
       <c r="H982" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>f545bc35-99c9-4adf-8768-649d8512c4ca</t>
+          <t>f52bff3e-a5ad-47c9-8eda-04fd6b2bddd5</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>ENG FELIPE</t>
+          <t>Robson Del Sante Cancelier</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>falar com atendente</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E983" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>RAFAELA PEREIRA DE MENEZES</t>
         </is>
       </c>
       <c r="F983" t="inlineStr">
@@ -37794,33 +37794,33 @@
         <v>1</v>
       </c>
       <c r="H983" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>f54d7f59-3cf1-4417-ad7f-2bcc5f8d8f0f</t>
+          <t>f545bc35-99c9-4adf-8768-649d8512c4ca</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
         <is>
-          <t>MARCOS CARDOZO</t>
+          <t>ENG FELIPE</t>
         </is>
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>falar com atendente</t>
         </is>
       </c>
       <c r="D984" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E984" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F984" t="inlineStr">
@@ -37832,28 +37832,28 @@
         <v>1</v>
       </c>
       <c r="H984" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>f5db1e46-87de-4c23-af1b-00292de7ddfb</t>
+          <t>f54d7f59-3cf1-4417-ad7f-2bcc5f8d8f0f</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Carlos Souza</t>
+          <t>MARCOS CARDOZO</t>
         </is>
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D985" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E985" t="inlineStr">
@@ -37870,28 +37870,28 @@
         <v>1</v>
       </c>
       <c r="H985" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>f5e3c091-761e-4341-a83f-11c02de1446f</t>
+          <t>f5db1e46-87de-4c23-af1b-00292de7ddfb</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>Caio Moreira</t>
+          <t>Carlos Souza</t>
         </is>
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E986" t="inlineStr">
@@ -37908,33 +37908,33 @@
         <v>1</v>
       </c>
       <c r="H986" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>f5e6b3e2-3f44-4603-9d14-e3e95f84bd7c</t>
+          <t>f5e3c091-761e-4341-a83f-11c02de1446f</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>Diogo Dantas</t>
+          <t>Caio Moreira</t>
         </is>
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D987" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
@@ -37946,18 +37946,18 @@
         <v>1</v>
       </c>
       <c r="H987" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>f5e8e506-ef2d-43be-97c9-83ffc78bb155</t>
+          <t>f5e6b3e2-3f44-4603-9d14-e3e95f84bd7c</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>Lucas Borges Silveira</t>
+          <t>Diogo Dantas</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -37967,12 +37967,12 @@
       </c>
       <c r="D988" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E988" t="inlineStr">
         <is>
-          <t>LUANA CASTILHO RIBEIRO</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F988" t="inlineStr">
@@ -37984,33 +37984,33 @@
         <v>1</v>
       </c>
       <c r="H988" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>f6129c12-5ece-4bf7-9802-c052b05e3e86</t>
+          <t>f5e8e506-ef2d-43be-97c9-83ffc78bb155</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Daniel Guimarães</t>
+          <t>Lucas Borges Silveira</t>
         </is>
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D989" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E989" t="inlineStr">
         <is>
-          <t>RAINEI TRINDADE DE SOUZA</t>
+          <t>LUANA CASTILHO RIBEIRO</t>
         </is>
       </c>
       <c r="F989" t="inlineStr">
@@ -38028,17 +38028,17 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>f6210d3c-bfaf-4dd4-99b9-a59509a4b40d</t>
+          <t>f6129c12-5ece-4bf7-9802-c052b05e3e86</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>Vinícius Oliveira</t>
+          <t>Daniel Guimarães</t>
         </is>
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Preciso falar com um atendente</t>
+          <t>Falar com comercial</t>
         </is>
       </c>
       <c r="D990" t="inlineStr">
@@ -38048,7 +38048,7 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>RAINEI TRINDADE DE SOUZA</t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
@@ -38060,33 +38060,33 @@
         <v>1</v>
       </c>
       <c r="H990" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>f65d046b-6af0-479e-a997-b52e0818ba1d</t>
+          <t>f6210d3c-bfaf-4dd4-99b9-a59509a4b40d</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
         <is>
-          <t>kayque taveira</t>
+          <t>Vinícius Oliveira</t>
         </is>
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Preciso falar com um atendente</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E991" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F991" t="inlineStr">
@@ -38098,18 +38098,18 @@
         <v>1</v>
       </c>
       <c r="H991" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>f6c1db4a-09d8-4e23-8ae7-2c5e80869e07</t>
+          <t>f65d046b-6af0-479e-a997-b52e0818ba1d</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
         <is>
-          <t>Thiago Barros</t>
+          <t>kayque taveira</t>
         </is>
       </c>
       <c r="C992" t="inlineStr">
@@ -38119,12 +38119,12 @@
       </c>
       <c r="D992" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E992" t="inlineStr">
         <is>
-          <t>MARCELO SOUZA FERREIRA DIAS</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F992" t="inlineStr">
@@ -38142,27 +38142,27 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>f705965e-2730-4f2f-9da8-790daad6e2c7</t>
+          <t>f6c1db4a-09d8-4e23-8ae7-2c5e80869e07</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
         <is>
-          <t>Larissa Xavier</t>
+          <t>Thiago Barros</t>
         </is>
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>gostaria de falar com um representante comercial</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E993" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>MARCELO SOUZA FERREIRA DIAS</t>
         </is>
       </c>
       <c r="F993" t="inlineStr">
@@ -38174,33 +38174,33 @@
         <v>1</v>
       </c>
       <c r="H993" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>f7942dc7-97d5-45bc-8d1c-337a923a8133</t>
+          <t>f705965e-2730-4f2f-9da8-790daad6e2c7</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>Felipe Avanci</t>
+          <t>Larissa Xavier</t>
         </is>
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>gostaria de falar com um representante comercial</t>
         </is>
       </c>
       <c r="D994" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E994" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F994" t="inlineStr">
@@ -38218,27 +38218,27 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>f7b49213-c1df-427b-8541-0e9d64845361</t>
+          <t>f7942dc7-97d5-45bc-8d1c-337a923a8133</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>BP ENGENHARIA</t>
+          <t>Felipe Avanci</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D995" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E995" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F995" t="inlineStr">
@@ -38256,27 +38256,27 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>f7c76366-4e8e-4e22-a83c-08009fb17843</t>
+          <t>f7b49213-c1df-427b-8541-0e9d64845361</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
         <is>
-          <t>AMANDA FLAVIO FERREIRA</t>
+          <t>BP ENGENHARIA</t>
         </is>
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Quero falar com vendedor</t>
+          <t>Falar com um atendente</t>
         </is>
       </c>
       <c r="D996" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>RAINEI TRINDADE DE SOUZA</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
@@ -38294,27 +38294,27 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>f7d535a4-f000-4588-825e-d02c6d23563d</t>
+          <t>f7c76366-4e8e-4e22-a83c-08009fb17843</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Robson Rocha</t>
+          <t>AMANDA FLAVIO FERREIRA</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
+          <t>Quero falar com vendedor</t>
         </is>
       </c>
       <c r="D997" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E997" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>RAINEI TRINDADE DE SOUZA</t>
         </is>
       </c>
       <c r="F997" t="inlineStr">
@@ -38332,22 +38332,22 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>f8394c71-58d7-4ee9-a652-e4fd5546b07c</t>
+          <t>f7d535a4-f000-4588-825e-d02c6d23563d</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>João Victor Marques da Mota</t>
+          <t>Robson Rocha</t>
         </is>
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Gostaria de falar com o meu vendedor</t>
+          <t>Falar com um atendente</t>
         </is>
       </c>
       <c r="D998" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E998" t="inlineStr">
@@ -38370,22 +38370,22 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>f8923c0a-661f-4c83-90f9-5c5b91c12b8d</t>
+          <t>f8394c71-58d7-4ee9-a652-e4fd5546b07c</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>JAILTON SOARES</t>
+          <t>João Victor Marques da Mota</t>
         </is>
       </c>
       <c r="C999" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Gostaria de falar com o meu vendedor</t>
         </is>
       </c>
       <c r="D999" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E999" t="inlineStr">
@@ -38408,27 +38408,27 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>f8c250e7-5d03-43cb-a92f-ba283c03239d</t>
+          <t>f8923c0a-661f-4c83-90f9-5c5b91c12b8d</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
         <is>
-          <t>Adriana Freitas</t>
+          <t>JAILTON SOARES</t>
         </is>
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>MARCELO SOUZA FERREIRA DIAS</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
@@ -38446,27 +38446,27 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>f8f0dd60-e36e-4871-b0b8-1cbdf301a21d</t>
+          <t>f8c250e7-5d03-43cb-a92f-ba283c03239d</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
         <is>
-          <t>ENERGYSOL ADMINISTRACAO LTDA</t>
+          <t>Adriana Freitas</t>
         </is>
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>MARCELO SOUZA FERREIRA DIAS</t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
@@ -38478,18 +38478,18 @@
         <v>1</v>
       </c>
       <c r="H1001" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>f97beb4e-6800-4779-95e8-dfecbaf9c470</t>
+          <t>f8f0dd60-e36e-4871-b0b8-1cbdf301a21d</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
         <is>
-          <t>FLAVIO DE OLIVEIRA</t>
+          <t>ENERGYSOL ADMINISTRACAO LTDA</t>
         </is>
       </c>
       <c r="C1002" t="inlineStr">
@@ -38499,12 +38499,12 @@
       </c>
       <c r="D1002" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E1002" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1002" t="inlineStr">
@@ -38516,33 +38516,33 @@
         <v>1</v>
       </c>
       <c r="H1002" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>f98f285d-fd4c-4480-bbe0-79fecb1bb07c</t>
+          <t>f97beb4e-6800-4779-95e8-dfecbaf9c470</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>JL GARCIA</t>
+          <t>FLAVIO DE OLIVEIRA</t>
         </is>
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1003" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F1003" t="inlineStr">
@@ -38554,33 +38554,33 @@
         <v>1</v>
       </c>
       <c r="H1003" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>f9aba2ac-42ba-431f-af50-ffa32ab9c61c</t>
+          <t>f98f285d-fd4c-4480-bbe0-79fecb1bb07c</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>Thiago Gualchi</t>
+          <t>JL GARCIA</t>
         </is>
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E1004" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F1004" t="inlineStr">
@@ -38598,22 +38598,22 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>f9fbae6e-9dff-44d2-9edd-8ef291de7667</t>
+          <t>f9aba2ac-42ba-431f-af50-ffa32ab9c61c</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Joao Ferro</t>
+          <t>Thiago Gualchi</t>
         </is>
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Falar com comercial</t>
         </is>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E1005" t="inlineStr">
@@ -38636,17 +38636,17 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>fa5a30e1-4dec-4084-8302-e03829d85ecc</t>
+          <t>f9fbae6e-9dff-44d2-9edd-8ef291de7667</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>Arisvan Costa</t>
+          <t>Joao Ferro</t>
         </is>
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1006" t="inlineStr">
@@ -38656,7 +38656,7 @@
       </c>
       <c r="E1006" t="inlineStr">
         <is>
-          <t>RAFAELA PEREIRA DE MENEZES</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1006" t="inlineStr">
@@ -38674,27 +38674,27 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>fa6d2c74-57e9-42f8-8849-ebd89b54003d</t>
+          <t>fa5a30e1-4dec-4084-8302-e03829d85ecc</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Murilo Silva</t>
+          <t>Arisvan Costa</t>
         </is>
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Falar com vendedor</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>RAFAELA PEREIRA DE MENEZES</t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
@@ -38712,27 +38712,27 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>fae8fa17-3005-4a79-872c-108a538cbafe</t>
+          <t>fa6d2c74-57e9-42f8-8849-ebd89b54003d</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>Icaro Lima</t>
+          <t>Murilo Silva</t>
         </is>
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Falar com vendedor</t>
         </is>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="E1008" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F1008" t="inlineStr">
@@ -38750,27 +38750,27 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>fba35019-c1fa-4831-a0d2-ff1a2d1f732b</t>
+          <t>fae8fa17-3005-4a79-872c-108a538cbafe</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Ze Horllando Silva Santos</t>
+          <t>Icaro Lima</t>
         </is>
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>falar com atendente</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1009" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1009" t="inlineStr">
@@ -38782,29 +38782,33 @@
         <v>1</v>
       </c>
       <c r="H1009" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>fc128bb6-5c76-47a9-b4c3-03e5f00008fc</t>
+          <t>fba35019-c1fa-4831-a0d2-ff1a2d1f732b</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>Ronan Silva e silva Silva</t>
+          <t>Ze Horllando Silva Santos</t>
         </is>
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
-        </is>
-      </c>
-      <c r="D1010" t="inlineStr"/>
+          <t>falar com atendente</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="E1010" t="inlineStr">
         <is>
-          <t>MARCELO SOUZA FERREIRA DIAS</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F1010" t="inlineStr">
@@ -38816,33 +38820,29 @@
         <v>1</v>
       </c>
       <c r="H1010" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>fc152faf-b634-4c6f-a689-4b924117cf3b</t>
+          <t>fc128bb6-5c76-47a9-b4c3-03e5f00008fc</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
         <is>
-          <t>rogerio nazareno</t>
+          <t>Ronan Silva e silva Silva</t>
         </is>
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
-        </is>
-      </c>
-      <c r="D1011" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
+          <t>Falar com um atendente</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr"/>
       <c r="E1011" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>MARCELO SOUZA FERREIRA DIAS</t>
         </is>
       </c>
       <c r="F1011" t="inlineStr">
@@ -38860,12 +38860,12 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>fc17d7cf-1544-4f97-b15e-94a6232ff369</t>
+          <t>fc152faf-b634-4c6f-a689-4b924117cf3b</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
         <is>
-          <t>Marlon Soares</t>
+          <t>rogerio nazareno</t>
         </is>
       </c>
       <c r="C1012" t="inlineStr">
@@ -38875,7 +38875,7 @@
       </c>
       <c r="D1012" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E1012" t="inlineStr">
@@ -38898,27 +38898,27 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>fc2ed842-032f-45ba-9349-e72d5908febf</t>
+          <t>fc17d7cf-1544-4f97-b15e-94a6232ff369</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>Douglas compras</t>
+          <t>Marlon Soares</t>
         </is>
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1013" t="inlineStr">
         <is>
-          <t>LUANA CASTILHO RIBEIRO</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F1013" t="inlineStr">
@@ -38930,33 +38930,33 @@
         <v>1</v>
       </c>
       <c r="H1013" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>fd01663c-e585-43ef-bb03-26e2d71a9468</t>
+          <t>fc2ed842-032f-45ba-9349-e72d5908febf</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>BRUNO LIM</t>
+          <t>Douglas compras</t>
         </is>
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>Consigo falar com vendedor direto ?</t>
+          <t>Falar com comercial</t>
         </is>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E1014" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>LUANA CASTILHO RIBEIRO</t>
         </is>
       </c>
       <c r="F1014" t="inlineStr">
@@ -38968,33 +38968,33 @@
         <v>1</v>
       </c>
       <c r="H1014" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>fd196893-9eb4-4111-a160-5a9a9c6dfa99</t>
+          <t>fd01663c-e585-43ef-bb03-26e2d71a9468</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
         <is>
-          <t>Rafael Aguiar</t>
+          <t>BRUNO LIM</t>
         </is>
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Falar com um vendedor</t>
+          <t>Consigo falar com vendedor direto ?</t>
         </is>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E1015" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1015" t="inlineStr">
@@ -39006,33 +39006,33 @@
         <v>1</v>
       </c>
       <c r="H1015" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>fd43f1ac-cdee-4058-8a51-385e97f6a9b7</t>
+          <t>fd196893-9eb4-4111-a160-5a9a9c6dfa99</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>IGOR RAFAEL</t>
+          <t>Rafael Aguiar</t>
         </is>
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Falar com um vendedor</t>
         </is>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1016" t="inlineStr">
         <is>
-          <t>RAINEI TRINDADE DE SOUZA</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F1016" t="inlineStr">
@@ -39050,12 +39050,12 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>fd9f2791-576e-4067-a735-5eee658c1755</t>
+          <t>fd43f1ac-cdee-4058-8a51-385e97f6a9b7</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>JASANIAS Silvestre</t>
+          <t>IGOR RAFAEL</t>
         </is>
       </c>
       <c r="C1017" t="inlineStr">
@@ -39065,12 +39065,12 @@
       </c>
       <c r="D1017" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E1017" t="inlineStr">
         <is>
-          <t>LUANA CASTILHO RIBEIRO</t>
+          <t>RAINEI TRINDADE DE SOUZA</t>
         </is>
       </c>
       <c r="F1017" t="inlineStr">
@@ -39088,17 +39088,17 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>fdcb8265-a7ee-49db-8866-1f23222638c0</t>
+          <t>fd9f2791-576e-4067-a735-5eee658c1755</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>Cleber Rodrigues Barboza</t>
+          <t>JASANIAS Silvestre</t>
         </is>
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
+          <t>Falar com comercial</t>
         </is>
       </c>
       <c r="D1018" t="inlineStr">
@@ -39108,7 +39108,7 @@
       </c>
       <c r="E1018" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>LUANA CASTILHO RIBEIRO</t>
         </is>
       </c>
       <c r="F1018" t="inlineStr">
@@ -39120,28 +39120,28 @@
         <v>1</v>
       </c>
       <c r="H1018" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>fe303d59-c03f-4058-b137-711b719c563a</t>
+          <t>fdcb8265-a7ee-49db-8866-1f23222638c0</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>George Santos</t>
+          <t>Cleber Rodrigues Barboza</t>
         </is>
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>falar com atendente</t>
+          <t>Falar com um atendente</t>
         </is>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E1019" t="inlineStr">
@@ -39158,28 +39158,28 @@
         <v>1</v>
       </c>
       <c r="H1019" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>fe7739d8-a596-4b89-8e3e-a36f53e99c67</t>
+          <t>fe303d59-c03f-4058-b137-711b719c563a</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>ykaro freitas</t>
+          <t>George Santos</t>
         </is>
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>preciso falar com o atendente</t>
+          <t>falar com atendente</t>
         </is>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1020" t="inlineStr">
@@ -39196,33 +39196,33 @@
         <v>1</v>
       </c>
       <c r="H1020" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>ff103c63-7b0c-420b-9e68-fbc928c6d374</t>
+          <t>fe7739d8-a596-4b89-8e3e-a36f53e99c67</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
         <is>
-          <t>manoel nunes</t>
+          <t>ykaro freitas</t>
         </is>
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Como é que faz pra falar com vendedor da Amaran?</t>
+          <t>preciso falar com o atendente</t>
         </is>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F1021" t="inlineStr">
@@ -39234,33 +39234,33 @@
         <v>1</v>
       </c>
       <c r="H1021" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>ff399760-c33c-4008-89af-2b95dc51b003</t>
+          <t>ff103c63-7b0c-420b-9e68-fbc928c6d374</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
         <is>
-          <t>Gustavo Leal</t>
+          <t>manoel nunes</t>
         </is>
       </c>
       <c r="C1022" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Como é que faz pra falar com vendedor da Amaran?</t>
         </is>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
@@ -39272,44 +39272,82 @@
         <v>1</v>
       </c>
       <c r="H1022" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
+          <t>ff399760-c33c-4008-89af-2b95dc51b003</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>Gustavo Leal</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Falar com comercial</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>KALILA DOS SANTOS CAETANO</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>DIGITAL</t>
+        </is>
+      </c>
+      <c r="G1023" t="b">
+        <v>1</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
           <t>ff4b2a31-ebeb-44ea-9dbf-2ea21632c1e3</t>
         </is>
       </c>
-      <c r="B1023" t="inlineStr">
+      <c r="B1024" t="inlineStr">
         <is>
           <t>Filipe Azeredo</t>
         </is>
       </c>
-      <c r="C1023" t="inlineStr">
+      <c r="C1024" t="inlineStr">
         <is>
           <t>Falar com comercial</t>
         </is>
       </c>
-      <c r="D1023" t="inlineStr">
+      <c r="D1024" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="E1023" t="inlineStr">
+      <c r="E1024" t="inlineStr">
         <is>
           <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
-      <c r="F1023" t="inlineStr">
-        <is>
-          <t>DIGITAL</t>
-        </is>
-      </c>
-      <c r="G1023" t="b">
-        <v>1</v>
-      </c>
-      <c r="H1023" t="n">
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>DIGITAL</t>
+        </is>
+      </c>
+      <c r="G1024" t="b">
+        <v>1</v>
+      </c>
+      <c r="H1024" t="n">
         <v>1</v>
       </c>
     </row>

--- a/output/relatorio.xlsx
+++ b/output/relatorio.xlsx
@@ -37333,7 +37333,7 @@
         <v>1</v>
       </c>
       <c r="H971" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="972">

--- a/output/relatorio.xlsx
+++ b/output/relatorio.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1153"/>
+  <dimension ref="A1:H1154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42665,27 +42665,27 @@
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>f5db1e46-87de-4c23-af1b-00292de7ddfb</t>
+          <t>f5d96c96-0dee-495e-8b43-2c536f7b864a</t>
         </is>
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Carlos Souza</t>
+          <t>Doglas Jose de Lima</t>
         </is>
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1112" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E1112" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F1112" t="inlineStr">
@@ -42697,28 +42697,28 @@
         <v>1</v>
       </c>
       <c r="H1112" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>f5e3c091-761e-4341-a83f-11c02de1446f</t>
+          <t>f5db1e46-87de-4c23-af1b-00292de7ddfb</t>
         </is>
       </c>
       <c r="B1113" t="inlineStr">
         <is>
-          <t>Caio Moreira</t>
+          <t>Carlos Souza</t>
         </is>
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1113" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1113" t="inlineStr">
@@ -42735,33 +42735,33 @@
         <v>1</v>
       </c>
       <c r="H1113" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>f5e6b3e2-3f44-4603-9d14-e3e95f84bd7c</t>
+          <t>f5e3c091-761e-4341-a83f-11c02de1446f</t>
         </is>
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Diogo Dantas</t>
+          <t>Caio Moreira</t>
         </is>
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1114" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E1114" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F1114" t="inlineStr">
@@ -42773,18 +42773,18 @@
         <v>1</v>
       </c>
       <c r="H1114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>f5e8e506-ef2d-43be-97c9-83ffc78bb155</t>
+          <t>f5e6b3e2-3f44-4603-9d14-e3e95f84bd7c</t>
         </is>
       </c>
       <c r="B1115" t="inlineStr">
         <is>
-          <t>Lucas Borges Silveira</t>
+          <t>Diogo Dantas</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
@@ -42794,12 +42794,12 @@
       </c>
       <c r="D1115" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1115" t="inlineStr">
         <is>
-          <t>LUANA CASTILHO RIBEIRO</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1115" t="inlineStr">
@@ -42811,33 +42811,33 @@
         <v>1</v>
       </c>
       <c r="H1115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>f6210d3c-bfaf-4dd4-99b9-a59509a4b40d</t>
+          <t>f5e8e506-ef2d-43be-97c9-83ffc78bb155</t>
         </is>
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Vinícius Oliveira</t>
+          <t>Lucas Borges Silveira</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Preciso falar com um atendente</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1116" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E1116" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>LUANA CASTILHO RIBEIRO</t>
         </is>
       </c>
       <c r="F1116" t="inlineStr">
@@ -42849,33 +42849,33 @@
         <v>1</v>
       </c>
       <c r="H1116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>f65d046b-6af0-479e-a997-b52e0818ba1d</t>
+          <t>f6210d3c-bfaf-4dd4-99b9-a59509a4b40d</t>
         </is>
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>kayque taveira</t>
+          <t>Vinícius Oliveira</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Preciso falar com um atendente</t>
         </is>
       </c>
       <c r="D1117" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1117" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F1117" t="inlineStr">
@@ -42887,18 +42887,18 @@
         <v>1</v>
       </c>
       <c r="H1117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>f6c1db4a-09d8-4e23-8ae7-2c5e80869e07</t>
+          <t>f65d046b-6af0-479e-a997-b52e0818ba1d</t>
         </is>
       </c>
       <c r="B1118" t="inlineStr">
         <is>
-          <t>Thiago Barros</t>
+          <t>kayque taveira</t>
         </is>
       </c>
       <c r="C1118" t="inlineStr">
@@ -42908,12 +42908,12 @@
       </c>
       <c r="D1118" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E1118" t="inlineStr">
         <is>
-          <t>MARCELO SOUZA FERREIRA DIAS</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F1118" t="inlineStr">
@@ -42931,27 +42931,27 @@
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>f705965e-2730-4f2f-9da8-790daad6e2c7</t>
+          <t>f6c1db4a-09d8-4e23-8ae7-2c5e80869e07</t>
         </is>
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Larissa Xavier</t>
+          <t>Thiago Barros</t>
         </is>
       </c>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>gostaria de falar com um representante comercial</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1119" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E1119" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>MARCELO SOUZA FERREIRA DIAS</t>
         </is>
       </c>
       <c r="F1119" t="inlineStr">
@@ -42963,33 +42963,33 @@
         <v>1</v>
       </c>
       <c r="H1119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>f78a7258-c9e9-4e84-b1e4-83b23980a1dd</t>
+          <t>f705965e-2730-4f2f-9da8-790daad6e2c7</t>
         </is>
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>DIEGO SILVA</t>
+          <t>Larissa Xavier</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
+          <t>gostaria de falar com um representante comercial</t>
         </is>
       </c>
       <c r="D1120" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E1120" t="inlineStr">
         <is>
-          <t>RAFAELA PEREIRA DE MENEZES</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F1120" t="inlineStr">
@@ -43001,33 +43001,33 @@
         <v>1</v>
       </c>
       <c r="H1120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>f7942dc7-97d5-45bc-8d1c-337a923a8133</t>
+          <t>f78a7258-c9e9-4e84-b1e4-83b23980a1dd</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
         <is>
-          <t>Felipe Avanci</t>
+          <t>DIEGO SILVA</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Falar com um atendente</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>RAFAELA PEREIRA DE MENEZES</t>
         </is>
       </c>
       <c r="F1121" t="inlineStr">
@@ -43039,33 +43039,33 @@
         <v>1</v>
       </c>
       <c r="H1121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>f7b49213-c1df-427b-8541-0e9d64845361</t>
+          <t>f7942dc7-97d5-45bc-8d1c-337a923a8133</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>BP ENGENHARIA</t>
+          <t>Felipe Avanci</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E1122" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F1122" t="inlineStr">
@@ -43083,27 +43083,27 @@
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>f7c76366-4e8e-4e22-a83c-08009fb17843</t>
+          <t>f7b49213-c1df-427b-8541-0e9d64845361</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>AMANDA FLAVIO FERREIRA</t>
+          <t>BP ENGENHARIA</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>Quero falar com vendedor</t>
+          <t>Falar com um atendente</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1123" t="inlineStr">
         <is>
-          <t>RAINEI TRINDADE DE SOUZA</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F1123" t="inlineStr">
@@ -43121,27 +43121,27 @@
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>f7d535a4-f000-4588-825e-d02c6d23563d</t>
+          <t>f7c76366-4e8e-4e22-a83c-08009fb17843</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Robson Rocha</t>
+          <t>AMANDA FLAVIO FERREIRA</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
+          <t>Quero falar com vendedor</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E1124" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>RAINEI TRINDADE DE SOUZA</t>
         </is>
       </c>
       <c r="F1124" t="inlineStr">
@@ -43159,27 +43159,27 @@
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>f83280b2-0b75-4a27-a87b-0c2f890920d4</t>
+          <t>f7d535a4-f000-4588-825e-d02c6d23563d</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>fabio ortiz meinberg</t>
+          <t>Robson Rocha</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>Falar com Humano</t>
+          <t>Falar com um atendente</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1125" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1125" t="inlineStr">
@@ -43197,27 +43197,27 @@
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>f8394c71-58d7-4ee9-a652-e4fd5546b07c</t>
+          <t>f83280b2-0b75-4a27-a87b-0c2f890920d4</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
         <is>
-          <t>João Victor Marques da Mota</t>
+          <t>fabio ortiz meinberg</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Gostaria de falar com o meu vendedor</t>
+          <t>Falar com Humano</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E1126" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F1126" t="inlineStr">
@@ -43235,22 +43235,22 @@
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>f8923c0a-661f-4c83-90f9-5c5b91c12b8d</t>
+          <t>f8394c71-58d7-4ee9-a652-e4fd5546b07c</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
         <is>
-          <t>JAILTON SOARES</t>
+          <t>João Victor Marques da Mota</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Gostaria de falar com o meu vendedor</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E1127" t="inlineStr">
@@ -43273,27 +43273,27 @@
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>f8c250e7-5d03-43cb-a92f-ba283c03239d</t>
+          <t>f8923c0a-661f-4c83-90f9-5c5b91c12b8d</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>Adriana Freitas</t>
+          <t>JAILTON SOARES</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1128" t="inlineStr">
         <is>
-          <t>MARCELO SOUZA FERREIRA DIAS</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1128" t="inlineStr">
@@ -43311,27 +43311,27 @@
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>f8f0dd60-e36e-4871-b0b8-1cbdf301a21d</t>
+          <t>f8c250e7-5d03-43cb-a92f-ba283c03239d</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>ENERGYSOL ADMINISTRACAO LTDA</t>
+          <t>Adriana Freitas</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1129" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="E1129" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>MARCELO SOUZA FERREIRA DIAS</t>
         </is>
       </c>
       <c r="F1129" t="inlineStr">
@@ -43343,18 +43343,18 @@
         <v>1</v>
       </c>
       <c r="H1129" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>f97beb4e-6800-4779-95e8-dfecbaf9c470</t>
+          <t>f8f0dd60-e36e-4871-b0b8-1cbdf301a21d</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>FLAVIO DE OLIVEIRA</t>
+          <t>ENERGYSOL ADMINISTRACAO LTDA</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
@@ -43364,12 +43364,12 @@
       </c>
       <c r="D1130" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="E1130" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1130" t="inlineStr">
@@ -43381,33 +43381,33 @@
         <v>1</v>
       </c>
       <c r="H1130" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>f98f285d-fd4c-4480-bbe0-79fecb1bb07c</t>
+          <t>f97beb4e-6800-4779-95e8-dfecbaf9c470</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>JL GARCIA</t>
+          <t>FLAVIO DE OLIVEIRA</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1131" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F1131" t="inlineStr">
@@ -43419,33 +43419,33 @@
         <v>1</v>
       </c>
       <c r="H1131" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>f9aba2ac-42ba-431f-af50-ffa32ab9c61c</t>
+          <t>f98f285d-fd4c-4480-bbe0-79fecb1bb07c</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Thiago Gualchi</t>
+          <t>JL GARCIA</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E1132" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F1132" t="inlineStr">
@@ -43463,22 +43463,22 @@
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>f9fbae6e-9dff-44d2-9edd-8ef291de7667</t>
+          <t>f9aba2ac-42ba-431f-af50-ffa32ab9c61c</t>
         </is>
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>Joao Ferro</t>
+          <t>Thiago Gualchi</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Falar com comercial</t>
         </is>
       </c>
       <c r="D1133" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
@@ -43501,27 +43501,27 @@
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>fa25cc9b-8caa-42c3-a8c0-25e376215e98</t>
+          <t>f9fbae6e-9dff-44d2-9edd-8ef291de7667</t>
         </is>
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>SOLARTEC ENERGIA SOLAR</t>
+          <t>Joao Ferro</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1134" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1134" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1134" t="inlineStr">
@@ -43539,27 +43539,27 @@
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>fa5a30e1-4dec-4084-8302-e03829d85ecc</t>
+          <t>fa25cc9b-8caa-42c3-a8c0-25e376215e98</t>
         </is>
       </c>
       <c r="B1135" t="inlineStr">
         <is>
-          <t>Arisvan Costa</t>
+          <t>SOLARTEC ENERGIA SOLAR</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
+          <t>Falar com um atendente</t>
         </is>
       </c>
       <c r="D1135" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="E1135" t="inlineStr">
         <is>
-          <t>RAFAELA PEREIRA DE MENEZES</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F1135" t="inlineStr">
@@ -43577,27 +43577,27 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>fa6d2c74-57e9-42f8-8849-ebd89b54003d</t>
+          <t>fa5a30e1-4dec-4084-8302-e03829d85ecc</t>
         </is>
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Murilo Silva</t>
+          <t>Arisvan Costa</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>Falar com vendedor</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
         <is>
-          <t>TO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1136" t="inlineStr">
         <is>
-          <t>VANESSA VIEIRA DE CARVALHO</t>
+          <t>RAFAELA PEREIRA DE MENEZES</t>
         </is>
       </c>
       <c r="F1136" t="inlineStr">
@@ -43615,27 +43615,27 @@
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>fae8fa17-3005-4a79-872c-108a538cbafe</t>
+          <t>fa6d2c74-57e9-42f8-8849-ebd89b54003d</t>
         </is>
       </c>
       <c r="B1137" t="inlineStr">
         <is>
-          <t>Icaro Lima</t>
+          <t>Murilo Silva</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>Falar com vendedor</t>
         </is>
       </c>
       <c r="D1137" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>TO</t>
         </is>
       </c>
       <c r="E1137" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
       <c r="F1137" t="inlineStr">
@@ -43653,27 +43653,27 @@
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>fba35019-c1fa-4831-a0d2-ff1a2d1f732b</t>
+          <t>fae8fa17-3005-4a79-872c-108a538cbafe</t>
         </is>
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>Ze Horllando Silva Santos</t>
+          <t>Icaro Lima</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>falar com atendente</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1138" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1138" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1138" t="inlineStr">
@@ -43685,29 +43685,33 @@
         <v>1</v>
       </c>
       <c r="H1138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>fc128bb6-5c76-47a9-b4c3-03e5f00008fc</t>
+          <t>fba35019-c1fa-4831-a0d2-ff1a2d1f732b</t>
         </is>
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>Ronan Silva e silva Silva</t>
+          <t>Ze Horllando Silva Santos</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
-        </is>
-      </c>
-      <c r="D1139" t="inlineStr"/>
+          <t>falar com atendente</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="E1139" t="inlineStr">
         <is>
-          <t>MARCELO SOUZA FERREIRA DIAS</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F1139" t="inlineStr">
@@ -43719,33 +43723,29 @@
         <v>1</v>
       </c>
       <c r="H1139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>fc152faf-b634-4c6f-a689-4b924117cf3b</t>
+          <t>fc128bb6-5c76-47a9-b4c3-03e5f00008fc</t>
         </is>
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>rogerio nazareno</t>
+          <t>Ronan Silva e silva Silva</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Quero falar com   meu   vendedor</t>
-        </is>
-      </c>
-      <c r="D1140" t="inlineStr">
-        <is>
-          <t>RJ</t>
-        </is>
-      </c>
+          <t>Falar com um atendente</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr"/>
       <c r="E1140" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>MARCELO SOUZA FERREIRA DIAS</t>
         </is>
       </c>
       <c r="F1140" t="inlineStr">
@@ -43763,12 +43763,12 @@
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>fc17d7cf-1544-4f97-b15e-94a6232ff369</t>
+          <t>fc152faf-b634-4c6f-a689-4b924117cf3b</t>
         </is>
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>Marlon Soares</t>
+          <t>rogerio nazareno</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
@@ -43778,7 +43778,7 @@
       </c>
       <c r="D1141" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="E1141" t="inlineStr">
@@ -43801,27 +43801,27 @@
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>fc2ed842-032f-45ba-9349-e72d5908febf</t>
+          <t>fc17d7cf-1544-4f97-b15e-94a6232ff369</t>
         </is>
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>Douglas compras</t>
+          <t>Marlon Soares</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Quero falar com   meu   vendedor</t>
         </is>
       </c>
       <c r="D1142" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1142" t="inlineStr">
         <is>
-          <t>LUANA CASTILHO RIBEIRO</t>
+          <t>KALILA DOS SANTOS CAETANO</t>
         </is>
       </c>
       <c r="F1142" t="inlineStr">
@@ -43833,33 +43833,33 @@
         <v>1</v>
       </c>
       <c r="H1142" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>fd01663c-e585-43ef-bb03-26e2d71a9468</t>
+          <t>fc2ed842-032f-45ba-9349-e72d5908febf</t>
         </is>
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>BRUNO LIM</t>
+          <t>Douglas compras</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Consigo falar com vendedor direto ?</t>
+          <t>Falar com comercial</t>
         </is>
       </c>
       <c r="D1143" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E1143" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>LUANA CASTILHO RIBEIRO</t>
         </is>
       </c>
       <c r="F1143" t="inlineStr">
@@ -43871,33 +43871,33 @@
         <v>1</v>
       </c>
       <c r="H1143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>fd196893-9eb4-4111-a160-5a9a9c6dfa99</t>
+          <t>fd01663c-e585-43ef-bb03-26e2d71a9468</t>
         </is>
       </c>
       <c r="B1144" t="inlineStr">
         <is>
-          <t>Rafael Aguiar</t>
+          <t>BRUNO LIM</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>Falar com um vendedor</t>
+          <t>Consigo falar com vendedor direto ?</t>
         </is>
       </c>
       <c r="D1144" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1144" t="inlineStr">
@@ -43909,33 +43909,33 @@
         <v>1</v>
       </c>
       <c r="H1144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>fd43f1ac-cdee-4058-8a51-385e97f6a9b7</t>
+          <t>fd196893-9eb4-4111-a160-5a9a9c6dfa99</t>
         </is>
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>IGOR RAFAEL</t>
+          <t>Rafael Aguiar</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Falar com um vendedor</t>
         </is>
       </c>
       <c r="D1145" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>RAINEI TRINDADE DE SOUZA</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F1145" t="inlineStr">
@@ -43947,18 +43947,18 @@
         <v>1</v>
       </c>
       <c r="H1145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>fd9f2791-576e-4067-a735-5eee658c1755</t>
+          <t>fd43f1ac-cdee-4058-8a51-385e97f6a9b7</t>
         </is>
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>JASANIAS Silvestre</t>
+          <t>IGOR RAFAEL</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
@@ -43968,12 +43968,12 @@
       </c>
       <c r="D1146" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>LUANA CASTILHO RIBEIRO</t>
+          <t>RAINEI TRINDADE DE SOUZA</t>
         </is>
       </c>
       <c r="F1146" t="inlineStr">
@@ -43991,17 +43991,17 @@
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>fdcb8265-a7ee-49db-8866-1f23222638c0</t>
+          <t>fd9f2791-576e-4067-a735-5eee658c1755</t>
         </is>
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>Cleber Rodrigues Barboza</t>
+          <t>JASANIAS Silvestre</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Falar com um atendente</t>
+          <t>Falar com comercial</t>
         </is>
       </c>
       <c r="D1147" t="inlineStr">
@@ -44011,7 +44011,7 @@
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>GABRIEL BORGES DOS SANTOS</t>
+          <t>LUANA CASTILHO RIBEIRO</t>
         </is>
       </c>
       <c r="F1147" t="inlineStr">
@@ -44023,28 +44023,28 @@
         <v>1</v>
       </c>
       <c r="H1147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>fe303d59-c03f-4058-b137-711b719c563a</t>
+          <t>fdcb8265-a7ee-49db-8866-1f23222638c0</t>
         </is>
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>George Santos</t>
+          <t>Cleber Rodrigues Barboza</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>falar com atendente</t>
+          <t>Falar com um atendente</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
@@ -44061,28 +44061,28 @@
         <v>1</v>
       </c>
       <c r="H1148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>fe7739d8-a596-4b89-8e3e-a36f53e99c67</t>
+          <t>fe303d59-c03f-4058-b137-711b719c563a</t>
         </is>
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>ykaro freitas</t>
+          <t>George Santos</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>preciso falar com o atendente</t>
+          <t>falar com atendente</t>
         </is>
       </c>
       <c r="D1149" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
@@ -44099,33 +44099,33 @@
         <v>1</v>
       </c>
       <c r="H1149" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>ff0172ed-78d5-44cb-94c2-9ffe30764b63</t>
+          <t>fe7739d8-a596-4b89-8e3e-a36f53e99c67</t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>Assinatura Energia</t>
+          <t>ykaro freitas</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Falar com atendente</t>
+          <t>preciso falar com o atendente</t>
         </is>
       </c>
       <c r="D1150" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
+          <t>GABRIEL BORGES DOS SANTOS</t>
         </is>
       </c>
       <c r="F1150" t="inlineStr">
@@ -44137,23 +44137,23 @@
         <v>1</v>
       </c>
       <c r="H1150" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>ff103c63-7b0c-420b-9e68-fbc928c6d374</t>
+          <t>ff0172ed-78d5-44cb-94c2-9ffe30764b63</t>
         </is>
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>manoel nunes</t>
+          <t>Assinatura Energia</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Como é que faz pra falar com vendedor da Amaran?</t>
+          <t>Falar com atendente</t>
         </is>
       </c>
       <c r="D1151" t="inlineStr">
@@ -44175,33 +44175,33 @@
         <v>1</v>
       </c>
       <c r="H1151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>ff399760-c33c-4008-89af-2b95dc51b003</t>
+          <t>ff103c63-7b0c-420b-9e68-fbc928c6d374</t>
         </is>
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>Gustavo Leal</t>
+          <t>manoel nunes</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Falar com comercial</t>
+          <t>Como é que faz pra falar com vendedor da Amaran?</t>
         </is>
       </c>
       <c r="D1152" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>KALILA DOS SANTOS CAETANO</t>
+          <t>ANDRESSA CLICIA DE JESUS SILVA</t>
         </is>
       </c>
       <c r="F1152" t="inlineStr">
@@ -44213,44 +44213,82 @@
         <v>1</v>
       </c>
       <c r="H1152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
+          <t>ff399760-c33c-4008-89af-2b95dc51b003</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Gustavo Leal</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Falar com comercial</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>KALILA DOS SANTOS CAETANO</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>DIGITAL</t>
+        </is>
+      </c>
+      <c r="G1153" t="b">
+        <v>1</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
           <t>ff4b2a31-ebeb-44ea-9dbf-2ea21632c1e3</t>
         </is>
       </c>
-      <c r="B1153" t="inlineStr">
+      <c r="B1154" t="inlineStr">
         <is>
           <t>Filipe Azeredo</t>
         </is>
       </c>
-      <c r="C1153" t="inlineStr">
+      <c r="C1154" t="inlineStr">
         <is>
           <t>Falar com comercial</t>
         </is>
       </c>
-      <c r="D1153" t="inlineStr">
+      <c r="D1154" t="inlineStr">
         <is>
           <t>TO</t>
         </is>
       </c>
-      <c r="E1153" t="inlineStr">
+      <c r="E1154" t="inlineStr">
         <is>
           <t>VANESSA VIEIRA DE CARVALHO</t>
         </is>
       </c>
-      <c r="F1153" t="inlineStr">
-        <is>
-          <t>DIGITAL</t>
-        </is>
-      </c>
-      <c r="G1153" t="b">
-        <v>1</v>
-      </c>
-      <c r="H1153" t="n">
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>DIGITAL</t>
+        </is>
+      </c>
+      <c r="G1154" t="b">
+        <v>1</v>
+      </c>
+      <c r="H1154" t="n">
         <v>1</v>
       </c>
     </row>
